--- a/实验设计/语义分析/语义表格/语义分析表.xlsx
+++ b/实验设计/语义分析/语义表格/语义分析表.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:474</t>
+          <t>src/语义分析/analyzer.cpp:470</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:474</t>
+          <t>src/语义分析/analyzer.cpp:470</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:433</t>
+          <t>src/语义分析/analyzer.cpp:429</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:451</t>
+          <t>src/语义分析/analyzer.cpp:447</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:355</t>
+          <t>src/语义分析/analyzer.cpp:351</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:527</t>
+          <t>src/语义分析/analyzer.cpp:523</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:569</t>
+          <t>src/语义分析/analyzer.cpp:565</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:355</t>
+          <t>src/语义分析/analyzer.cpp:351</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:319</t>
+          <t>src/语义分析/analyzer.cpp:315</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>函数实参数量与原型不一致</t>
+          <t>函数实参数量与签名不一致</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:C58"/>
+  <dimension ref="A2:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -6721,34 +6721,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEM_OPERANDS</t>
+          <t>SEM_ASSIGN_TYPE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>if (integer_compound &amp;&amp; detail::floating(source)) { error(node, "位运算和取余需要整型操作数", "SEM_OPERANDS"); return; }</t>
+          <t>if (!can_assign(left-&gt;type, right-&gt;type)) { error(node, "赋值需要不允许的隐式类型转换", "SEM_ASSIGN_TYPE"); return; }</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:312</t>
+          <t>src/语义分析/analyzer.cpp:309</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEM_ASSIGN_TYPE</t>
+          <t>SEM_ADDRESS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>if (!can_assign(left-&gt;type, source)) { error(node, "赋值需要不允许的隐式类型转换", "SEM_ASSIGN_TYPE"); return; }</t>
+          <t>if (!address_allowed) { error(node, "&amp; 只允许用在 scanf 的输入参数中", "SEM_ADDRESS"); return; }</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:313</t>
+          <t>src/语义分析/analyzer.cpp:321</t>
         </is>
       </c>
     </row>
@@ -6760,58 +6760,58 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>if (!address_allowed) { error(node, "&amp; 只允许用在 scanf 的输入参数中", "SEM_ADDRESS"); return; }</t>
+          <t>error(node, "取地址需要对象左值；scanf 还需要可修改的数值对象", "SEM_ADDRESS"); return;</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:325</t>
+          <t>src/语义分析/analyzer.cpp:324</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEM_ADDRESS</t>
+          <t>SEM_POINTER_REMOVED</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>error(node, "取地址需要对象左值；scanf 还需要可修改的数值对象", "SEM_ADDRESS"); return;</t>
+          <t>error(node, "本项目不支持解引用", "SEM_POINTER_REMOVED"); return;</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:328</t>
+          <t>src/语义分析/analyzer.cpp:331</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEM_POINTER_REMOVED</t>
+          <t>SEM_LVALUE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>error(node, "本项目不支持解引用", "SEM_POINTER_REMOVED"); return;</t>
+          <t>error(node, "自增或自减需要可修改变量", "SEM_LVALUE"); return;</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:335</t>
+          <t>src/语义分析/analyzer.cpp:338</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEM_LVALUE</t>
+          <t>SEM_OPERANDS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>error(node, "自增或自减需要可修改变量", "SEM_LVALUE"); return;</t>
+          <t>if (node.name == "~" &amp;&amp; detail::floating(child-&gt;type)) { error(node, "按位取反需要整型", "SEM_OPERANDS"); return; }</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6823,34 +6823,34 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEM_OPERANDS</t>
+          <t>SEM_CALL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>if (node.name == "~" &amp;&amp; detail::floating(child-&gt;type)) { error(node, "按位取反需要整型", "SEM_OPERANDS"); return; }</t>
+          <t>if (callee.kind != NodeType::Identifier || callee.category != ValueCategory::Function) { error(node, "调用需要函数名字", "SEM_CALL"); return; }</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:346</t>
+          <t>src/语义分析/analyzer.cpp:356</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEM_CALL</t>
+          <t>SEM_FORMAT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>if (callee.kind != NodeType::Identifier || callee.category != ValueCategory::Function) { error(node, "调用需要函数名字", "SEM_CALL"); return; }</t>
+          <t>!valid_expression(*node.children[1])) { error(node, "M1 输入输出需要字面量格式串", "SEM_FORMAT"); return; }</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:360</t>
+          <t>src/语义分析/analyzer.cpp:369</t>
         </is>
       </c>
     </row>
@@ -6862,80 +6862,80 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>!valid_expression(*node.children[1])) { error(node, "M1 输入输出需要字面量格式串", "SEM_FORMAT"); return; }</t>
+          <t>} catch (const std::exception&amp; exception) { error(node, exception.what(), "SEM_FORMAT"); return; }</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:373</t>
+          <t>src/语义分析/analyzer.cpp:396</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEM_FORMAT</t>
+          <t>SEM_ARGUMENT_COUNT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>} catch (const std::exception&amp; exception) { error(node, exception.what(), "SEM_FORMAT"); return; }</t>
+          <t>error(node, "函数实参数量与签名不一致", "SEM_ARGUMENT_COUNT"); return;</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:400</t>
+          <t>src/语义分析/analyzer.cpp:399</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEM_ARGUMENT_COUNT</t>
+          <t>SEM_ARGUMENT_TYPE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>error(node, "函数实参数量与签名不一致", "SEM_ARGUMENT_COUNT"); return;</t>
+          <t>if (!assignable(target, *node.children[i])) error(node, "函数实参类型不兼容", "SEM_ARGUMENT_TYPE");</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:403</t>
+          <t>src/语义分析/analyzer.cpp:405</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEM_ARGUMENT_TYPE</t>
+          <t>SEM_DEPTH</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>if (!assignable(target, *node.children[i])) error(node, "函数实参类型不兼容", "SEM_ARGUMENT_TYPE");</t>
+          <t>diagnostics_.report(Level::Fatal, node.range, "语法树嵌套过深", "SEM_DEPTH");</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:409</t>
+          <t>src/语义分析/analyzer.cpp:418</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEM_DEPTH</t>
+          <t>SEM_INDEX</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>diagnostics_.report(Level::Fatal, node.range, "语法树嵌套过深", "SEM_DEPTH");</t>
+          <t>error(node, "下标访问需要数组和整型下标", "SEM_INDEX"); break;</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:422</t>
+          <t>src/语义分析/analyzer.cpp:436</t>
         </is>
       </c>
     </row>
@@ -6947,29 +6947,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>error(node, "下标访问需要数组和整型下标", "SEM_INDEX"); break;</t>
+          <t>catch (const std::runtime_error&amp; exception) { error(node, exception.what(), "SEM_INDEX"); break; }</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:440</t>
+          <t>src/语义分析/analyzer.cpp:439</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEM_INDEX</t>
+          <t>SEM_MEMBER</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>catch (const std::runtime_error&amp; exception) { error(node, exception.what(), "SEM_INDEX"); break; }</t>
+          <t>if (object.type-&gt;kind != TypeKind::Struct) { error(node, "成员访问需要结构体对象", "SEM_MEMBER"); break; }</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:443</t>
+          <t>src/语义分析/analyzer.cpp:452</t>
         </is>
       </c>
     </row>
@@ -6981,114 +6981,114 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>if (object.type-&gt;kind != TypeKind::Struct) { error(node, "成员访问需要结构体对象", "SEM_MEMBER"); break; }</t>
+          <t>if (!index) { error(node, "结构体中没有该成员：" + node.name, "SEM_MEMBER"); break; }</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:456</t>
+          <t>src/语义分析/analyzer.cpp:454</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEM_MEMBER</t>
+          <t>SEM_UNSUPPORTED</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>if (!index) { error(node, "结构体中没有该成员：" + node.name, "SEM_MEMBER"); break; }</t>
+          <t>default: error(node, "此表达式节点尚未支持，或语法树已被分析过", "SEM_UNSUPPORTED"); break;</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:458</t>
+          <t>src/语义分析/analyzer.cpp:463</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEM_UNSUPPORTED</t>
+          <t>SEM_FUNCTION_VALUE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>default: error(node, "此表达式节点尚未支持，或语法树已被分析过", "SEM_UNSUPPORTED"); break;</t>
+          <t>error(node, "函数名字只能用于直接调用", "SEM_FUNCTION_VALUE");</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:467</t>
+          <t>src/语义分析/analyzer.cpp:466</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEM_FUNCTION_VALUE</t>
+          <t>SEM_DECL_TYPE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>error(node, "函数名字只能用于直接调用", "SEM_FUNCTION_VALUE");</t>
+          <t>catch (const std::runtime_error&amp; exception) { error(node, exception.what(), "SEM_DECL_TYPE"); return; }</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:470</t>
+          <t>src/语义分析/analyzer.cpp:482</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEM_DECL_TYPE</t>
+          <t>SEM_CONST_INIT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>catch (const std::runtime_error&amp; exception) { error(node, exception.what(), "SEM_DECL_TYPE"); return; }</t>
+          <t>} else if (node.type-&gt;is_const) error(node, "const 变量必须初始化", "SEM_CONST_INIT");</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:486</t>
+          <t>src/语义分析/analyzer.cpp:495</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEM_CONST_INIT</t>
+          <t>SEM_DEPTH</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>} else if (node.type-&gt;is_const) error(node, "const 变量必须初始化", "SEM_CONST_INIT");</t>
+          <t>diagnostics_.report(Level::Fatal, node.range, "语法树嵌套过深", "SEM_DEPTH");</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:499</t>
+          <t>src/语义分析/analyzer.cpp:503</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEM_DEPTH</t>
+          <t>SEM_RETURN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>diagnostics_.report(Level::Fatal, node.range, "语法树嵌套过深", "SEM_DEPTH");</t>
+          <t>if (return_type_-&gt;kind != TypeKind::Void) error(node, "非 void 函数必须返回一个值", "SEM_RETURN");</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:507</t>
+          <t>src/语义分析/analyzer.cpp:526</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>if (return_type_-&gt;kind != TypeKind::Void) error(node, "非 void 函数必须返回一个值", "SEM_RETURN");</t>
+          <t>if (return_type_-&gt;kind == TypeKind::Void) error(node, "void 函数不能返回一个值", "SEM_RETURN");</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:530</t>
+          <t>src/语义分析/analyzer.cpp:529</t>
         </is>
       </c>
     </row>
@@ -7117,165 +7117,148 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>if (return_type_-&gt;kind == TypeKind::Void) error(node, "void 函数不能返回一个值", "SEM_RETURN");</t>
+          <t>if (!assignable(return_type_, *node.children[0])) error(node, "返回值类型不兼容", "SEM_RETURN");</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:533</t>
+          <t>src/语义分析/analyzer.cpp:531</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEM_RETURN</t>
+          <t>SEM_LOOP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>if (!assignable(return_type_, *node.children[0])) error(node, "返回值类型不兼容", "SEM_RETURN");</t>
+          <t>error(node, "break 和 continue 只能用在循环中", "SEM_LOOP");</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:535</t>
+          <t>src/语义分析/analyzer.cpp:567</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEM_LOOP</t>
+          <t>SEM_UNSUPPORTED</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>error(node, "break 和 continue 只能用在循环中", "SEM_LOOP");</t>
+          <t>default: error(node, "此语句节点尚未支持", "SEM_UNSUPPORTED"); break;</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:571</t>
+          <t>src/语义分析/analyzer.cpp:570</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEM_UNSUPPORTED</t>
+          <t>SEM_FUNCTION</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>default: error(node, "此语句节点尚未支持", "SEM_UNSUPPORTED"); break;</t>
+          <t>error(node, "M1 函数类型或形参列表无效", "SEM_FUNCTION"); return;</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:574</t>
+          <t>src/语义分析/analyzer.cpp:595</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEM_FUNCTION</t>
+          <t>SEM_PARAMETER</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>error(node, "M1 函数类型或形参列表无效", "SEM_FUNCTION"); return;</t>
+          <t>error(node, "函数形参节点与签名不一致", "SEM_PARAMETER"); return;</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:599</t>
+          <t>src/语义分析/analyzer.cpp:606</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEM_PARAMETER</t>
+          <t>SEM_MISSING_RETURN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>error(node, "函数形参节点与签名不一致", "SEM_PARAMETER"); return;</t>
+          <t>error(node, "非 void 函数必须保证所有路径返回；请在末尾添加 return", "SEM_MISSING_RETURN");</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:610</t>
+          <t>src/语义分析/analyzer.cpp:642</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEM_MISSING_RETURN</t>
+          <t>SEM_ROOT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>error(node, "非 void 函数必须保证所有路径返回；请在末尾添加 return", "SEM_MISSING_RETURN");</t>
+          <t>diagnostics_.report(Level::Fatal, program.range, "语义分析需要 Program 根节点", "SEM_ROOT");</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:646</t>
+          <t>src/语义分析/analyzer.cpp:652</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEM_ROOT</t>
+          <t>SEM_UNSUPPORTED</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>diagnostics_.report(Level::Fatal, program.range, "语义分析需要 Program 根节点", "SEM_ROOT");</t>
+          <t>else error(*child, "M1 顶层仅支持变量和函数定义", "SEM_UNSUPPORTED");</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>src/语义分析/analyzer.cpp:656</t>
+          <t>src/语义分析/analyzer.cpp:662</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEM_UNSUPPORTED</t>
+          <t>SEM_UNDEFINED_FUNCTION</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>else error(*child, "M1 顶层仅支持变量和函数定义", "SEM_UNSUPPORTED");</t>
+          <t>diagnostics_.report(Level::Error, call.second, "被调用函数没有定义：" + table_.symbol(call.first)-&gt;name, "SEM_UNDEFINED_FUNCTION");</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
           <t>src/语义分析/analyzer.cpp:666</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>SEM_UNDEFINED_FUNCTION</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>diagnostics_.report(Level::Error, call.second, "被调用函数没有定义：" + table_.symbol(call.first)-&gt;name, "SEM_UNDEFINED_FUNCTION");</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>src/语义分析/analyzer.cpp:670</t>
         </is>
       </c>
     </row>
